--- a/medical_consent_forms/022_nasal_flu_vaccine_consent_form--medical_consent_forms.xlsx
+++ b/medical_consent_forms/022_nasal_flu_vaccine_consent_form--medical_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vaccine_info</t>
+          <t>vaccine_info_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vaccine Information</t>
+          <t>Vaccine Info 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Medical Conditions 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>allergies_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Allergies 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>allergies_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>allergies_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
